--- a/docs/modulo3/Flujo de Caja.xlsx
+++ b/docs/modulo3/Flujo de Caja.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="305">
   <si>
     <t>Presupuesto Integrado Proyecto Automatización</t>
   </si>
@@ -426,6 +426,9 @@
     <t>Organización de cableado</t>
   </si>
   <si>
+    <t>≤</t>
+  </si>
+  <si>
     <t xml:space="preserve">Software y herramientas de desarrollo </t>
   </si>
   <si>
@@ -579,6 +582,9 @@
     <t>Subtotal software, pruebas y logística</t>
   </si>
   <si>
+    <t>Costos Directos (COP)</t>
+  </si>
+  <si>
     <t>5. Mano de obra directa (EDT)</t>
   </si>
   <si>
@@ -615,12 +621,18 @@
     <t>Imprevistos / refinamiento- 5%</t>
   </si>
   <si>
+    <t>Mano de obra directa (EDT)</t>
+  </si>
+  <si>
     <t>Subtotal Mano de obra</t>
   </si>
   <si>
     <t>Utilidad integrador-10%</t>
   </si>
   <si>
+    <t>Servicios públicos y SST</t>
+  </si>
+  <si>
     <t>6. Servicios públicos y SST</t>
   </si>
   <si>
@@ -633,12 +645,18 @@
     <t xml:space="preserve">Total </t>
   </si>
   <si>
+    <t>Subtotal Costos Directos</t>
+  </si>
+  <si>
     <t>Agua, limpieza y disposición</t>
   </si>
   <si>
     <t>Estimación de ejecución</t>
   </si>
   <si>
+    <t>Costos indirectos y administrativos</t>
+  </si>
+  <si>
     <t>Internet / red temporal</t>
   </si>
   <si>
@@ -648,6 +666,9 @@
     <t>Total linea 2</t>
   </si>
   <si>
+    <t>Total Presupuesto Base</t>
+  </si>
+  <si>
     <t>SST, permisos, señalización y EPP</t>
   </si>
   <si>
@@ -679,11 +700,6 @@
   </si>
   <si>
     <t>Total linea 3</t>
-  </si>
-  <si>
-    <t>El presente presupuesto del proyecto de automatización se elaboró siguiendo un enfoque de estimación ascendente por paquetes de trabajo (EDT), con la lógica de una empresa integradora. Se descompuso el alcance en equipos mecánicos y celda de paletizado, control y seguridad, eléctrico/neumático, software, pruebas y logística, consolidando los costos hacia arriba para obtener subtotales por categoría. Posteriormente se separaron los costos directos (equipos, software, pruebas, consumibles, mano de obra y servicios públicos) y se sumaron los indirectos, imprevistos y la utilidad del integrador. Los costos directos ascienden a 763.922.450 COP, incluyendo mano de obra directa calculada con base en horas estimadas por estudiante y por disciplina (Ingeniería Industrial, Automatización, PLC, Simulación y SCADA), tomando referencias de tarifas promedio de mercado para proyectos de ingeniería industrial y automatización en Colombia.                        
-Sobre los costos directos se aplican costos indirectos y administrativos, que representan la gestión integral del proyecto, administración, imprevistos y la utilidad del integrador. Estos se calcularon aplicando porcentajes estándar sobre la suma de los costos directos: costos indirectos de proyecto 6% (45.835.347 COP), administración y generales 12% (91.670.694 COP), imprevistos/refinamiento 5% (38.196.123 COP) y utilidad integrador 10% (76.392.245 COP). Se consideró que los imprevistos incluyen incertidumbres inherentes a sistemas industriales, posibles ajustes de integración y refinamiento de costos ascendentes. La aplicación de estos porcentajes sigue normas internacionales de gestión de proyectos (PMBOK® Guide – Seventh Edition) y estándares de seguridad funcional (ISO 13849, ISA-95).                        
-El presupuesto total base asciende a 1.016.016.859 COP, sin incluir IVA, garantizando la cobertura completa del proyecto. Para la estimación se consideraron precios de mercado actualizados de sistemas de paletizado (ABB IRB 460, 110 kg carga, 2,4 m alcance), conversión de monedas según TRM COP/USD 3.704,87 y EUR/COP 4.309,87 (23-mar-2026), tarifas eléctricas industriales Enel, y referencias de proveedores de PLC, HMI, sensores y software. La planificación excluye la construcción de nuevas líneas de llenado/seamer, enfocándose en la automatización del paletizado, integración de control/OEE-MES lite y ajustes mecánicos del dry-end, manteniendo el resto de la línea existente. Por línea y solo considerando equipos, software y pruebas, el subtotal asciende a 746.700.000 COP, reflejando la inversión directa necesaria para la implementación técnica del proyecto.</t>
   </si>
   <si>
     <t>Total</t>
@@ -1159,7 +1175,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="87">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1282,7 +1298,13 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
     <xf borderId="4" fillId="0" fontId="4" numFmtId="3" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
     <xf borderId="4" fillId="0" fontId="4" numFmtId="9" xfId="0" applyBorder="1" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
@@ -1627,9 +1649,9 @@
     <col customWidth="1" min="22" max="22" width="31.38"/>
     <col customWidth="1" min="23" max="23" width="7.0"/>
     <col customWidth="1" min="24" max="24" width="9.75"/>
-    <col customWidth="1" min="25" max="25" width="17.0"/>
-    <col customWidth="1" min="26" max="26" width="17.13"/>
-    <col customWidth="1" min="27" max="27" width="26.13"/>
+    <col customWidth="1" min="25" max="25" width="30.88"/>
+    <col customWidth="1" min="26" max="26" width="24.13"/>
+    <col customWidth="1" min="27" max="27" width="29.88"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3104,7 +3126,9 @@
       <c r="V26" s="21"/>
       <c r="W26" s="21"/>
       <c r="X26" s="21"/>
-      <c r="Y26" s="21"/>
+      <c r="Y26" s="20" t="s">
+        <v>137</v>
+      </c>
       <c r="Z26" s="22">
         <v>8000000.0</v>
       </c>
@@ -3113,7 +3137,7 @@
     </row>
     <row r="27">
       <c r="B27" s="33" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
@@ -3123,7 +3147,7 @@
       <c r="H27" s="3"/>
       <c r="L27" s="37"/>
       <c r="M27" s="14" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N27" s="14">
         <v>1.0</v>
@@ -3139,14 +3163,14 @@
         <v>10000000</v>
       </c>
       <c r="R27" s="7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="T27" s="38"/>
       <c r="U27" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="V27" s="7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="W27" s="7">
         <v>1.0</v>
@@ -3161,20 +3185,20 @@
         <v>5.96E7</v>
       </c>
       <c r="AA27" s="7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AC27" s="10"/>
     </row>
     <row r="28">
       <c r="B28" s="34" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C28" s="33" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D28" s="3"/>
       <c r="E28" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F28" s="35">
         <v>1.0</v>
@@ -3188,7 +3212,7 @@
       </c>
       <c r="L28" s="37"/>
       <c r="M28" s="14" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N28" s="14">
         <v>2.0</v>
@@ -3204,11 +3228,11 @@
         <v>1100000</v>
       </c>
       <c r="R28" s="7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="T28" s="21"/>
       <c r="U28" s="20" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="V28" s="21"/>
       <c r="W28" s="21"/>
@@ -3222,14 +3246,14 @@
     </row>
     <row r="29">
       <c r="B29" s="34" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C29" s="33" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D29" s="3"/>
       <c r="E29" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F29" s="35">
         <v>1.0</v>
@@ -3242,7 +3266,7 @@
         <v>0</v>
       </c>
       <c r="L29" s="13" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M29" s="27"/>
       <c r="N29" s="27"/>
@@ -3254,7 +3278,7 @@
       </c>
       <c r="R29" s="20"/>
       <c r="S29" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="T29" s="38"/>
       <c r="U29" s="7" t="s">
@@ -3281,14 +3305,14 @@
     </row>
     <row r="30">
       <c r="B30" s="34" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C30" s="33" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D30" s="3"/>
       <c r="E30" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F30" s="35">
         <v>1.0</v>
@@ -3301,10 +3325,10 @@
         <v>0</v>
       </c>
       <c r="L30" s="13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M30" s="14" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N30" s="14">
         <v>1.0</v>
@@ -3320,14 +3344,14 @@
         <v>1900000</v>
       </c>
       <c r="R30" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="T30" s="38"/>
       <c r="U30" s="7" t="s">
         <v>53</v>
       </c>
       <c r="V30" s="7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="W30" s="7">
         <v>1.0</v>
@@ -3342,19 +3366,19 @@
         <v>1.22E7</v>
       </c>
       <c r="AA30" s="7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="34" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C31" s="33" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D31" s="3"/>
       <c r="E31" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F31" s="35">
         <v>1.0</v>
@@ -3368,7 +3392,7 @@
       </c>
       <c r="L31" s="37"/>
       <c r="M31" s="14" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N31" s="14">
         <v>1.0</v>
@@ -3384,14 +3408,14 @@
         <v>1100000</v>
       </c>
       <c r="R31" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="T31" s="38"/>
       <c r="U31" s="7" t="s">
         <v>53</v>
       </c>
       <c r="V31" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="W31" s="7">
         <v>1.0</v>
@@ -3406,20 +3430,20 @@
         <v>2500000.0</v>
       </c>
       <c r="AA31" s="7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AC31" s="10"/>
     </row>
     <row r="32">
       <c r="B32" s="34" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C32" s="33" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D32" s="3"/>
       <c r="E32" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F32" s="35">
         <v>1.0</v>
@@ -3433,7 +3457,7 @@
       </c>
       <c r="L32" s="37"/>
       <c r="M32" s="14" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N32" s="14">
         <v>1.0</v>
@@ -3449,14 +3473,14 @@
         <v>4600000</v>
       </c>
       <c r="R32" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="T32" s="38"/>
       <c r="U32" s="7" t="s">
         <v>53</v>
       </c>
       <c r="V32" s="7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="W32" s="7">
         <v>1.0</v>
@@ -3471,19 +3495,19 @@
         <v>3.5E7</v>
       </c>
       <c r="AA32" s="7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="34" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C33" s="33" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D33" s="3"/>
       <c r="E33" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F33" s="35">
         <v>1.0</v>
@@ -3497,7 +3521,7 @@
       </c>
       <c r="L33" s="37"/>
       <c r="M33" s="14" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N33" s="14">
         <v>1.0</v>
@@ -3513,7 +3537,7 @@
         <v>4600000</v>
       </c>
       <c r="R33" s="7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="T33" s="21"/>
       <c r="U33" s="20" t="s">
@@ -3530,14 +3554,14 @@
     </row>
     <row r="34">
       <c r="B34" s="34" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C34" s="33" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D34" s="3"/>
       <c r="E34" s="35" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F34" s="35">
         <v>1.0</v>
@@ -3551,7 +3575,7 @@
       </c>
       <c r="L34" s="37"/>
       <c r="M34" s="14" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N34" s="14">
         <v>1.0</v>
@@ -3567,7 +3591,7 @@
         <v>3000000</v>
       </c>
       <c r="R34" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="T34" s="25"/>
       <c r="U34" s="24" t="s">
@@ -3584,7 +3608,7 @@
     </row>
     <row r="35">
       <c r="B35" s="41" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" s="2"/>
@@ -3594,7 +3618,7 @@
       <c r="H35" s="3"/>
       <c r="L35" s="37"/>
       <c r="M35" s="14" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N35" s="14">
         <v>1.0</v>
@@ -3610,10 +3634,10 @@
         <v>2500000</v>
       </c>
       <c r="R35" s="7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="T35" s="20" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="U35" s="21"/>
       <c r="V35" s="21"/>
@@ -3624,15 +3648,15 @@
         <v>7.46898675E8</v>
       </c>
       <c r="AA35" s="20" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="16" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C36" s="41" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="42"/>
@@ -3648,7 +3672,7 @@
       </c>
       <c r="L36" s="37"/>
       <c r="M36" s="14" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N36" s="14">
         <v>1.0</v>
@@ -3664,7 +3688,7 @@
         <v>35000000</v>
       </c>
       <c r="R36" s="7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="T36" s="43"/>
       <c r="U36" s="43"/>
@@ -3677,10 +3701,10 @@
     </row>
     <row r="37">
       <c r="B37" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="C37" s="41" t="s">
         <v>186</v>
-      </c>
-      <c r="C37" s="41" t="s">
-        <v>185</v>
       </c>
       <c r="D37" s="3"/>
       <c r="E37" s="42"/>
@@ -3695,7 +3719,7 @@
         <v>400000</v>
       </c>
       <c r="L37" s="13" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M37" s="27"/>
       <c r="N37" s="27"/>
@@ -3706,13 +3730,18 @@
         <v>52700000</v>
       </c>
       <c r="R37" s="20"/>
-      <c r="AA37" s="43"/>
+      <c r="Y37" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z37" s="44" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="38">
       <c r="C38" s="10"/>
       <c r="D38" s="10"/>
       <c r="L38" s="13" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="M38" s="14" t="s">
         <v>79</v>
@@ -3721,7 +3750,7 @@
         <v>140.0</v>
       </c>
       <c r="O38" s="14" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P38" s="15">
         <v>17045.0</v>
@@ -3731,14 +3760,20 @@
         <v>2386300</v>
       </c>
       <c r="R38" s="7" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="T38" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="U38" s="44">
+        <v>193</v>
+      </c>
+      <c r="U38" s="45">
         <f>Z10</f>
         <v>31400000</v>
+      </c>
+      <c r="Y38" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="Z38" s="46">
+        <v>5.923E8</v>
       </c>
       <c r="AA38" s="43"/>
     </row>
@@ -3753,7 +3788,7 @@
         <v>85.0</v>
       </c>
       <c r="O39" s="14" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P39" s="15">
         <v>18750.0</v>
@@ -3763,14 +3798,20 @@
         <v>1593750</v>
       </c>
       <c r="R39" s="7" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="T39" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="U39" s="44">
+        <v>195</v>
+      </c>
+      <c r="U39" s="45">
         <f>U38+Q43+Q48</f>
         <v>44262450</v>
+      </c>
+      <c r="Y39" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z39" s="46">
+        <v>4.646E7</v>
       </c>
       <c r="AA39" s="43"/>
     </row>
@@ -3783,7 +3824,7 @@
         <v>50.0</v>
       </c>
       <c r="O40" s="14" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P40" s="15">
         <v>18750.0</v>
@@ -3793,14 +3834,20 @@
         <v>937500</v>
       </c>
       <c r="R40" s="7" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="T40" s="14" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="U40" s="14">
         <f>$U$39*0.06</f>
         <v>2655747</v>
+      </c>
+      <c r="Y40" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="Z40" s="46">
+        <v>5.96E7</v>
       </c>
       <c r="AA40" s="43"/>
     </row>
@@ -3813,7 +3860,7 @@
         <v>50.0</v>
       </c>
       <c r="O41" s="14" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P41" s="15">
         <v>17898.0</v>
@@ -3823,14 +3870,20 @@
         <v>894900</v>
       </c>
       <c r="R41" s="7" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="T41" s="14" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="U41" s="14">
         <f>$U$39*0.12</f>
         <v>5311494</v>
+      </c>
+      <c r="Y41" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z41" s="46">
+        <v>5.27E7</v>
       </c>
       <c r="AA41" s="43"/>
     </row>
@@ -3843,7 +3896,7 @@
         <v>40.0</v>
       </c>
       <c r="O42" s="14" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="P42" s="15">
         <v>18750.0</v>
@@ -3853,20 +3906,26 @@
         <v>750000</v>
       </c>
       <c r="R42" s="7" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="T42" s="14" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="U42" s="14">
         <f>$U$39*0.05</f>
         <v>2213122.5</v>
       </c>
+      <c r="Y42" s="23" t="s">
+        <v>202</v>
+      </c>
+      <c r="Z42" s="46">
+        <v>6562450.0</v>
+      </c>
       <c r="AA42" s="43"/>
     </row>
     <row r="43">
       <c r="L43" s="13" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="M43" s="27"/>
       <c r="N43" s="27"/>
@@ -3878,20 +3937,26 @@
       </c>
       <c r="R43" s="20"/>
       <c r="T43" s="14" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="U43" s="14">
         <f>$U$39*0.1</f>
         <v>4426245</v>
       </c>
+      <c r="Y43" s="23" t="s">
+        <v>205</v>
+      </c>
+      <c r="Z43" s="46">
+        <v>6300000.0</v>
+      </c>
       <c r="AA43" s="43"/>
     </row>
     <row r="44">
       <c r="L44" s="13" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="M44" s="14" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="N44" s="14">
         <v>1.0</v>
@@ -3907,21 +3972,27 @@
         <v>2900000</v>
       </c>
       <c r="R44" s="7" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="T44" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="U44" s="44">
+        <v>209</v>
+      </c>
+      <c r="U44" s="45">
         <f>SUM(U39:U43)</f>
         <v>58869058.5</v>
+      </c>
+      <c r="Y44" s="23" t="s">
+        <v>210</v>
+      </c>
+      <c r="Z44" s="46">
+        <v>7.6392245E8</v>
       </c>
       <c r="AA44" s="43"/>
     </row>
     <row r="45">
       <c r="L45" s="37"/>
       <c r="M45" s="14" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="N45" s="14">
         <v>1.0</v>
@@ -3937,14 +4008,20 @@
         <v>850000</v>
       </c>
       <c r="R45" s="7" t="s">
-        <v>207</v>
+        <v>212</v>
+      </c>
+      <c r="Y45" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="Z45" s="46">
+        <v>2.52094409E8</v>
       </c>
       <c r="AA45" s="43"/>
     </row>
     <row r="46">
       <c r="L46" s="37"/>
       <c r="M46" s="14" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="N46" s="14">
         <v>1.0</v>
@@ -3960,21 +4037,27 @@
         <v>350000</v>
       </c>
       <c r="R46" s="7" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="T46" s="14" t="s">
-        <v>210</v>
-      </c>
-      <c r="U46" s="44">
+        <v>216</v>
+      </c>
+      <c r="U46" s="45">
         <f>Z19</f>
         <v>27700000</v>
+      </c>
+      <c r="Y46" s="23" t="s">
+        <v>217</v>
+      </c>
+      <c r="Z46" s="46">
+        <v>1.016016859E9</v>
       </c>
       <c r="AA46" s="43"/>
     </row>
     <row r="47">
       <c r="L47" s="19"/>
       <c r="M47" s="14" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="N47" s="14">
         <v>1.0</v>
@@ -3990,12 +4073,12 @@
         <v>2200000</v>
       </c>
       <c r="R47" s="7" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="T47" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="U47" s="44">
+        <v>195</v>
+      </c>
+      <c r="U47" s="45">
         <f>Q43+Q48+U46</f>
         <v>40562450</v>
       </c>
@@ -4003,7 +4086,7 @@
     </row>
     <row r="48">
       <c r="L48" s="13" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="M48" s="27"/>
       <c r="N48" s="27"/>
@@ -4015,9 +4098,9 @@
       </c>
       <c r="R48" s="20"/>
       <c r="T48" s="14" t="s">
-        <v>195</v>
-      </c>
-      <c r="U48" s="44">
+        <v>197</v>
+      </c>
+      <c r="U48" s="45">
         <f>$U$47*0.06</f>
         <v>2433747</v>
       </c>
@@ -4025,25 +4108,25 @@
     </row>
     <row r="49">
       <c r="L49" s="13" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="M49" s="14" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="N49" s="37"/>
       <c r="O49" s="37"/>
-      <c r="P49" s="45"/>
+      <c r="P49" s="47"/>
       <c r="Q49" s="15">
         <f>SUM($Q$48+$Q$43+$Q$37+$Q$29+$Q$22+$Q$11)*0.06</f>
         <v>45835347</v>
       </c>
       <c r="R49" s="7" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="T49" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="U49" s="44">
+        <v>199</v>
+      </c>
+      <c r="U49" s="45">
         <f>$U$47*0.12</f>
         <v>4867494</v>
       </c>
@@ -4053,22 +4136,22 @@
       <c r="A50" s="10"/>
       <c r="L50" s="37"/>
       <c r="M50" s="14" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="N50" s="37"/>
       <c r="O50" s="37"/>
-      <c r="P50" s="45"/>
+      <c r="P50" s="47"/>
       <c r="Q50" s="15">
         <f>SUM($Q$48+$Q$43+$Q$37+$Q$29+$Q$22+$Q$11)*0.12</f>
         <v>91670694</v>
       </c>
       <c r="R50" s="7" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="T50" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="U50" s="44">
+        <v>201</v>
+      </c>
+      <c r="U50" s="45">
         <f>$U$47*0.05</f>
         <v>2028122.5</v>
       </c>
@@ -4077,22 +4160,22 @@
     <row r="51">
       <c r="L51" s="37"/>
       <c r="M51" s="14" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="N51" s="37"/>
       <c r="O51" s="37"/>
-      <c r="P51" s="45"/>
+      <c r="P51" s="47"/>
       <c r="Q51" s="15">
         <f>SUM($Q$48+$Q$43+$Q$37+$Q$29+$Q$22+$Q$11)*0.05</f>
         <v>38196122.5</v>
       </c>
       <c r="R51" s="7" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="T51" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="U51" s="44">
+        <v>204</v>
+      </c>
+      <c r="U51" s="45">
         <f>$U$47*0.1</f>
         <v>4056245</v>
       </c>
@@ -4101,7 +4184,7 @@
     <row r="52">
       <c r="L52" s="19"/>
       <c r="M52" s="14" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="N52" s="37"/>
       <c r="O52" s="37"/>
@@ -4111,12 +4194,12 @@
         <v>76392245</v>
       </c>
       <c r="R52" s="7" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="T52" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="U52" s="44">
+        <v>209</v>
+      </c>
+      <c r="U52" s="45">
         <f>SUM(U47:U51)</f>
         <v>53948058.5</v>
       </c>
@@ -4124,7 +4207,7 @@
     </row>
     <row r="53">
       <c r="L53" s="13" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="M53" s="27"/>
       <c r="N53" s="27"/>
@@ -4135,113 +4218,201 @@
         <v>1016016859</v>
       </c>
       <c r="R53" s="20" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="AA53" s="43"/>
     </row>
     <row r="54">
       <c r="T54" s="14" t="s">
-        <v>221</v>
-      </c>
-      <c r="U54" s="44">
+        <v>228</v>
+      </c>
+      <c r="U54" s="45">
         <f>Z34</f>
         <v>572800000</v>
       </c>
       <c r="AA54" s="43"/>
     </row>
     <row r="55">
-      <c r="L55" s="46" t="s">
-        <v>222</v>
-      </c>
+      <c r="L55" s="48"/>
+      <c r="M55" s="48"/>
+      <c r="N55" s="48"/>
+      <c r="O55" s="48"/>
+      <c r="P55" s="48"/>
+      <c r="Q55" s="48"/>
+      <c r="R55" s="48"/>
       <c r="T55" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="U55" s="44">
+        <v>195</v>
+      </c>
+      <c r="U55" s="45">
         <f>Q43+Q48+U54</f>
         <v>585662450</v>
       </c>
       <c r="AA55" s="43"/>
     </row>
     <row r="56">
+      <c r="L56" s="48"/>
+      <c r="M56" s="48"/>
+      <c r="N56" s="48"/>
+      <c r="O56" s="48"/>
+      <c r="P56" s="48"/>
+      <c r="Q56" s="48"/>
+      <c r="R56" s="48"/>
       <c r="T56" s="14" t="s">
-        <v>195</v>
-      </c>
-      <c r="U56" s="44">
+        <v>197</v>
+      </c>
+      <c r="U56" s="45">
         <f>$U$55*0.06</f>
         <v>35139747</v>
       </c>
       <c r="AA56" s="43"/>
     </row>
     <row r="57">
+      <c r="L57" s="48"/>
+      <c r="M57" s="48"/>
+      <c r="N57" s="48"/>
+      <c r="O57" s="48"/>
+      <c r="P57" s="48"/>
+      <c r="Q57" s="48"/>
+      <c r="R57" s="48"/>
       <c r="T57" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="U57" s="44">
+        <v>199</v>
+      </c>
+      <c r="U57" s="45">
         <f>$U$55*0.12</f>
         <v>70279494</v>
       </c>
       <c r="AA57" s="43"/>
     </row>
     <row r="58">
+      <c r="L58" s="48"/>
+      <c r="M58" s="48"/>
+      <c r="N58" s="48"/>
+      <c r="O58" s="48"/>
+      <c r="P58" s="48"/>
+      <c r="Q58" s="48"/>
+      <c r="R58" s="48"/>
       <c r="T58" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="U58" s="44">
+        <v>201</v>
+      </c>
+      <c r="U58" s="45">
         <f>$U$55*0.05</f>
         <v>29283122.5</v>
       </c>
       <c r="AA58" s="43"/>
     </row>
     <row r="59">
+      <c r="L59" s="48"/>
+      <c r="M59" s="48"/>
+      <c r="N59" s="48"/>
+      <c r="O59" s="48"/>
+      <c r="P59" s="48"/>
+      <c r="Q59" s="48"/>
+      <c r="R59" s="48"/>
       <c r="T59" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="U59" s="44">
+        <v>204</v>
+      </c>
+      <c r="U59" s="45">
         <f>$U$55*0.1</f>
         <v>58566245</v>
       </c>
       <c r="AA59" s="43"/>
     </row>
     <row r="60">
+      <c r="L60" s="48"/>
+      <c r="M60" s="48"/>
+      <c r="N60" s="48"/>
+      <c r="O60" s="48"/>
+      <c r="P60" s="48"/>
+      <c r="Q60" s="48"/>
+      <c r="R60" s="48"/>
       <c r="T60" s="14" t="s">
-        <v>223</v>
-      </c>
-      <c r="U60" s="44">
+        <v>229</v>
+      </c>
+      <c r="U60" s="45">
         <f>SUM(U55:U59)</f>
         <v>778931058.5</v>
       </c>
       <c r="AA60" s="43"/>
     </row>
     <row r="61">
+      <c r="L61" s="48"/>
+      <c r="M61" s="48"/>
+      <c r="N61" s="48"/>
+      <c r="O61" s="48"/>
+      <c r="P61" s="48"/>
+      <c r="Q61" s="48"/>
+      <c r="R61" s="48"/>
       <c r="AA61" s="43"/>
     </row>
     <row r="62">
+      <c r="L62" s="48"/>
+      <c r="M62" s="48"/>
+      <c r="N62" s="48"/>
+      <c r="O62" s="48"/>
+      <c r="P62" s="48"/>
+      <c r="Q62" s="48"/>
+      <c r="R62" s="48"/>
       <c r="AA62" s="43"/>
     </row>
     <row r="63">
+      <c r="L63" s="48"/>
+      <c r="M63" s="48"/>
+      <c r="N63" s="48"/>
+      <c r="O63" s="48"/>
+      <c r="P63" s="48"/>
+      <c r="Q63" s="48"/>
+      <c r="R63" s="48"/>
       <c r="AA63" s="43"/>
     </row>
     <row r="64">
+      <c r="L64" s="48"/>
+      <c r="M64" s="48"/>
+      <c r="N64" s="48"/>
+      <c r="O64" s="48"/>
+      <c r="P64" s="48"/>
+      <c r="Q64" s="48"/>
+      <c r="R64" s="48"/>
       <c r="AA64" s="43"/>
     </row>
     <row r="65">
+      <c r="L65" s="48"/>
+      <c r="M65" s="48"/>
+      <c r="N65" s="48"/>
+      <c r="O65" s="48"/>
+      <c r="P65" s="48"/>
+      <c r="Q65" s="48"/>
+      <c r="R65" s="48"/>
       <c r="AA65" s="43"/>
     </row>
     <row r="66">
+      <c r="L66" s="48"/>
+      <c r="M66" s="48"/>
+      <c r="N66" s="48"/>
+      <c r="O66" s="48"/>
+      <c r="P66" s="48"/>
+      <c r="Q66" s="48"/>
+      <c r="R66" s="48"/>
       <c r="AA66" s="43"/>
     </row>
     <row r="67">
+      <c r="L67" s="48"/>
+      <c r="M67" s="48"/>
+      <c r="N67" s="48"/>
+      <c r="O67" s="48"/>
+      <c r="P67" s="48"/>
+      <c r="Q67" s="48"/>
+      <c r="R67" s="48"/>
       <c r="AA67" s="43"/>
     </row>
     <row r="68">
       <c r="AA68" s="43"/>
     </row>
     <row r="69">
-      <c r="B69" s="47" t="s">
-        <v>224</v>
-      </c>
-      <c r="C69" s="48" t="s">
-        <v>225</v>
+      <c r="B69" s="49" t="s">
+        <v>230</v>
+      </c>
+      <c r="C69" s="50" t="s">
+        <v>231</v>
       </c>
       <c r="D69" s="2"/>
       <c r="E69" s="2"/>
@@ -7133,32 +7304,8 @@
     <row r="1030">
       <c r="AA1030" s="43"/>
     </row>
-    <row r="1031">
-      <c r="AA1031" s="43"/>
-    </row>
-    <row r="1032">
-      <c r="AA1032" s="43"/>
-    </row>
-    <row r="1033">
-      <c r="AA1033" s="43"/>
-    </row>
-    <row r="1034">
-      <c r="AA1034" s="43"/>
-    </row>
-    <row r="1035">
-      <c r="AA1035" s="43"/>
-    </row>
-    <row r="1036">
-      <c r="AA1036" s="43"/>
-    </row>
-    <row r="1037">
-      <c r="AA1037" s="43"/>
-    </row>
-    <row r="1038">
-      <c r="AA1038" s="43"/>
-    </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="29">
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="C19:D19"/>
@@ -7172,7 +7319,6 @@
     <mergeCell ref="C36:D36"/>
     <mergeCell ref="C37:D37"/>
     <mergeCell ref="C69:H69"/>
-    <mergeCell ref="L55:R67"/>
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="B27:H27"/>
     <mergeCell ref="C28:D28"/>
@@ -7214,50 +7360,50 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="49" t="s">
-        <v>226</v>
+      <c r="A1" s="51" t="s">
+        <v>232</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="3"/>
-      <c r="F1" s="49" t="s">
-        <v>227</v>
+      <c r="F1" s="51" t="s">
+        <v>233</v>
       </c>
       <c r="G1" s="3"/>
-      <c r="I1" s="49" t="s">
-        <v>228</v>
+      <c r="I1" s="51" t="s">
+        <v>234</v>
       </c>
       <c r="J1" s="3"/>
     </row>
     <row r="2">
-      <c r="A2" s="50" t="s">
-        <v>229</v>
-      </c>
-      <c r="B2" s="50" t="s">
-        <v>230</v>
-      </c>
-      <c r="C2" s="51" t="s">
-        <v>231</v>
-      </c>
-      <c r="D2" s="51" t="s">
-        <v>232</v>
-      </c>
-      <c r="F2" s="52" t="s">
-        <v>233</v>
+      <c r="A2" s="52" t="s">
+        <v>235</v>
+      </c>
+      <c r="B2" s="52" t="s">
+        <v>236</v>
+      </c>
+      <c r="C2" s="53" t="s">
+        <v>237</v>
+      </c>
+      <c r="D2" s="53" t="s">
+        <v>238</v>
+      </c>
+      <c r="F2" s="54" t="s">
+        <v>239</v>
       </c>
       <c r="G2" s="14" t="s">
-        <v>234</v>
-      </c>
-      <c r="I2" s="53">
+        <v>240</v>
+      </c>
+      <c r="I2" s="55">
         <v>1000.0</v>
       </c>
-      <c r="J2" s="53">
+      <c r="J2" s="55">
         <v>1.0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="52" t="s">
-        <v>235</v>
+      <c r="A3" s="54" t="s">
+        <v>241</v>
       </c>
       <c r="B3" s="14">
         <v>2.185E7</v>
@@ -7270,22 +7416,22 @@
         <f>B27*C3/0.1</f>
         <v>56.76</v>
       </c>
-      <c r="F3" s="52" t="s">
-        <v>236</v>
+      <c r="F3" s="54" t="s">
+        <v>242</v>
       </c>
       <c r="G3" s="14">
         <v>1.32</v>
       </c>
-      <c r="I3" s="54" t="s">
-        <v>237</v>
-      </c>
-      <c r="J3" s="54" t="s">
-        <v>238</v>
+      <c r="I3" s="56" t="s">
+        <v>243</v>
+      </c>
+      <c r="J3" s="56" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="52" t="s">
-        <v>239</v>
+      <c r="A4" s="54" t="s">
+        <v>245</v>
       </c>
       <c r="B4" s="14">
         <v>4227600.0</v>
@@ -7296,16 +7442,16 @@
       <c r="D4" s="14">
         <v>0.0</v>
       </c>
-      <c r="F4" s="52" t="s">
-        <v>240</v>
+      <c r="F4" s="54" t="s">
+        <v>246</v>
       </c>
       <c r="G4" s="14">
         <v>1.36</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="52" t="s">
-        <v>241</v>
+      <c r="A5" s="54" t="s">
+        <v>247</v>
       </c>
       <c r="B5" s="14">
         <v>3.572E7</v>
@@ -7317,8 +7463,8 @@
         <f>B43*C5/0.1</f>
         <v>73.5</v>
       </c>
-      <c r="I5" s="49" t="s">
-        <v>242</v>
+      <c r="I5" s="51" t="s">
+        <v>248</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -7326,150 +7472,150 @@
       <c r="M5" s="3"/>
     </row>
     <row r="6">
-      <c r="F6" s="49" t="s">
-        <v>243</v>
+      <c r="F6" s="51" t="s">
+        <v>249</v>
       </c>
       <c r="G6" s="3"/>
-      <c r="I6" s="51" t="s">
-        <v>244</v>
-      </c>
-      <c r="J6" s="51" t="s">
-        <v>235</v>
-      </c>
-      <c r="K6" s="51" t="s">
-        <v>245</v>
-      </c>
-      <c r="L6" s="51" t="s">
-        <v>246</v>
-      </c>
-      <c r="M6" s="51" t="s">
-        <v>223</v>
+      <c r="I6" s="53" t="s">
+        <v>250</v>
+      </c>
+      <c r="J6" s="53" t="s">
+        <v>241</v>
+      </c>
+      <c r="K6" s="53" t="s">
+        <v>251</v>
+      </c>
+      <c r="L6" s="53" t="s">
+        <v>252</v>
+      </c>
+      <c r="M6" s="53" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="7">
-      <c r="F7" s="52" t="s">
-        <v>247</v>
-      </c>
-      <c r="G7" s="55">
+      <c r="F7" s="54" t="s">
+        <v>253</v>
+      </c>
+      <c r="G7" s="57">
         <v>12734.31</v>
       </c>
-      <c r="I7" s="51" t="s">
-        <v>248</v>
-      </c>
-      <c r="J7" s="56">
+      <c r="I7" s="53" t="s">
+        <v>254</v>
+      </c>
+      <c r="J7" s="58">
         <f>12*G7+((B3*C3*(G4-0.36))/1000)*G8</f>
         <v>52416229.42</v>
       </c>
-      <c r="K7" s="56">
+      <c r="K7" s="58">
         <f>12*G7+((B4*C4*(G4-0.36))/1000)*G8</f>
         <v>404787573.9</v>
       </c>
-      <c r="L7" s="56">
+      <c r="L7" s="58">
         <f>12*G7+((B5*C5*(G4-0.36))/1000)*G8</f>
         <v>271102049.5</v>
       </c>
-      <c r="M7" s="56">
+      <c r="M7" s="58">
         <f t="shared" ref="M7:M8" si="1">J7+K7+L7</f>
         <v>728305852.9</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="49" t="s">
-        <v>249</v>
+      <c r="A8" s="51" t="s">
+        <v>255</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="3"/>
-      <c r="F8" s="52" t="s">
-        <v>250</v>
-      </c>
-      <c r="G8" s="55">
+      <c r="F8" s="54" t="s">
+        <v>256</v>
+      </c>
+      <c r="G8" s="57">
         <v>5056.91</v>
       </c>
-      <c r="I8" s="51" t="s">
-        <v>251</v>
-      </c>
-      <c r="J8" s="56">
+      <c r="I8" s="53" t="s">
+        <v>257</v>
+      </c>
+      <c r="J8" s="58">
         <f>(B3*D3/1000)*G9</f>
         <v>4365525120</v>
       </c>
-      <c r="K8" s="55">
+      <c r="K8" s="57">
         <v>0.0</v>
       </c>
-      <c r="L8" s="56">
+      <c r="L8" s="58">
         <f>(B5*D5/1000)*G9</f>
         <v>9241478400</v>
       </c>
-      <c r="M8" s="56">
+      <c r="M8" s="58">
         <f t="shared" si="1"/>
         <v>13607003520</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="50" t="s">
-        <v>229</v>
-      </c>
-      <c r="B9" s="50" t="s">
-        <v>252</v>
-      </c>
-      <c r="C9" s="50" t="s">
-        <v>253</v>
-      </c>
-      <c r="D9" s="51" t="s">
-        <v>254</v>
-      </c>
-      <c r="F9" s="52" t="s">
-        <v>255</v>
-      </c>
-      <c r="G9" s="57">
+      <c r="A9" s="52" t="s">
+        <v>235</v>
+      </c>
+      <c r="B9" s="52" t="s">
+        <v>258</v>
+      </c>
+      <c r="C9" s="52" t="s">
+        <v>259</v>
+      </c>
+      <c r="D9" s="53" t="s">
+        <v>260</v>
+      </c>
+      <c r="F9" s="54" t="s">
+        <v>261</v>
+      </c>
+      <c r="G9" s="59">
         <v>3520.0</v>
       </c>
-      <c r="I9" s="51" t="s">
-        <v>256</v>
-      </c>
-      <c r="J9" s="56"/>
-      <c r="K9" s="56"/>
-      <c r="L9" s="56"/>
-      <c r="M9" s="56"/>
+      <c r="I9" s="53" t="s">
+        <v>262</v>
+      </c>
+      <c r="J9" s="58"/>
+      <c r="K9" s="58"/>
+      <c r="L9" s="58"/>
+      <c r="M9" s="58"/>
     </row>
     <row r="10">
       <c r="A10" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="B10" s="57">
+        <v>263</v>
+      </c>
+      <c r="B10" s="59">
         <v>8500.0</v>
       </c>
-      <c r="C10" s="57">
+      <c r="C10" s="59">
         <v>7000.0</v>
       </c>
-      <c r="D10" s="58">
+      <c r="D10" s="60">
         <f t="shared" ref="D10:D12" si="2">C10*0.54</f>
         <v>3780</v>
       </c>
-      <c r="I10" s="51" t="s">
-        <v>258</v>
-      </c>
-      <c r="J10" s="56"/>
-      <c r="K10" s="56"/>
-      <c r="L10" s="56"/>
-      <c r="M10" s="56"/>
+      <c r="I10" s="53" t="s">
+        <v>264</v>
+      </c>
+      <c r="J10" s="58"/>
+      <c r="K10" s="58"/>
+      <c r="L10" s="58"/>
+      <c r="M10" s="58"/>
     </row>
     <row r="11">
-      <c r="A11" s="59" t="s">
-        <v>239</v>
-      </c>
-      <c r="B11" s="57">
+      <c r="A11" s="61" t="s">
+        <v>245</v>
+      </c>
+      <c r="B11" s="59">
         <v>15000.0</v>
       </c>
-      <c r="C11" s="57">
+      <c r="C11" s="59">
         <v>12600.0</v>
       </c>
-      <c r="D11" s="58">
+      <c r="D11" s="60">
         <f t="shared" si="2"/>
         <v>6804</v>
       </c>
-      <c r="I11" s="49" t="s">
-        <v>259</v>
+      <c r="I11" s="51" t="s">
+        <v>265</v>
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
@@ -7478,38 +7624,38 @@
     </row>
     <row r="12">
       <c r="A12" s="14" t="s">
-        <v>241</v>
-      </c>
-      <c r="B12" s="57">
+        <v>247</v>
+      </c>
+      <c r="B12" s="59">
         <v>4500.0</v>
       </c>
-      <c r="C12" s="57">
+      <c r="C12" s="59">
         <v>3750.0</v>
       </c>
-      <c r="D12" s="58">
+      <c r="D12" s="60">
         <f t="shared" si="2"/>
         <v>2025</v>
       </c>
-      <c r="I12" s="51" t="s">
-        <v>260</v>
-      </c>
-      <c r="J12" s="60"/>
-      <c r="K12" s="60"/>
-      <c r="L12" s="60"/>
-      <c r="M12" s="60"/>
+      <c r="I12" s="53" t="s">
+        <v>266</v>
+      </c>
+      <c r="J12" s="62"/>
+      <c r="K12" s="62"/>
+      <c r="L12" s="62"/>
+      <c r="M12" s="62"/>
     </row>
     <row r="13">
-      <c r="I13" s="51" t="s">
-        <v>261</v>
-      </c>
-      <c r="J13" s="60"/>
-      <c r="K13" s="60"/>
-      <c r="L13" s="60"/>
-      <c r="M13" s="60"/>
+      <c r="I13" s="53" t="s">
+        <v>267</v>
+      </c>
+      <c r="J13" s="62"/>
+      <c r="K13" s="62"/>
+      <c r="L13" s="62"/>
+      <c r="M13" s="62"/>
     </row>
     <row r="14">
-      <c r="I14" s="49" t="s">
-        <v>262</v>
+      <c r="I14" s="51" t="s">
+        <v>268</v>
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
@@ -7517,121 +7663,121 @@
       <c r="M14" s="3"/>
     </row>
     <row r="15">
-      <c r="A15" s="49" t="s">
-        <v>240</v>
+      <c r="A15" s="51" t="s">
+        <v>246</v>
       </c>
       <c r="B15" s="3"/>
-      <c r="I15" s="51" t="s">
-        <v>248</v>
-      </c>
-      <c r="J15" s="61">
+      <c r="I15" s="53" t="s">
+        <v>254</v>
+      </c>
+      <c r="J15" s="63">
         <f>12*G7+((B3*C3*(G4-1))/1000)*G8</f>
         <v>18967642.09</v>
       </c>
-      <c r="K15" s="61">
+      <c r="K15" s="63">
         <f>12*G7+((B4*C4*(G4-1))/1000)*G8</f>
         <v>145821326.1</v>
       </c>
-      <c r="L15" s="61">
+      <c r="L15" s="63">
         <f>12*G7+((B5*C5*(G4-1))/1000)*G8</f>
         <v>97694537.33</v>
       </c>
-      <c r="M15" s="61">
+      <c r="M15" s="63">
         <f>SUM(J15:L15)</f>
         <v>262483505.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="s">
-        <v>263</v>
-      </c>
-      <c r="B16" s="62">
+        <v>269</v>
+      </c>
+      <c r="B16" s="64">
         <v>0.46</v>
       </c>
-      <c r="I16" s="51" t="s">
-        <v>264</v>
-      </c>
-      <c r="J16" s="63"/>
-      <c r="K16" s="63"/>
-      <c r="L16" s="63"/>
-      <c r="M16" s="63"/>
+      <c r="I16" s="53" t="s">
+        <v>270</v>
+      </c>
+      <c r="J16" s="65"/>
+      <c r="K16" s="65"/>
+      <c r="L16" s="65"/>
+      <c r="M16" s="65"/>
     </row>
     <row r="17">
       <c r="A17" s="14" t="s">
-        <v>265</v>
-      </c>
-      <c r="B17" s="64">
+        <v>271</v>
+      </c>
+      <c r="B17" s="66">
         <v>0.088</v>
       </c>
-      <c r="I17" s="51" t="s">
-        <v>266</v>
-      </c>
-      <c r="J17" s="63"/>
-      <c r="K17" s="63"/>
-      <c r="L17" s="63"/>
-      <c r="M17" s="63"/>
+      <c r="I17" s="53" t="s">
+        <v>272</v>
+      </c>
+      <c r="J17" s="65"/>
+      <c r="K17" s="65"/>
+      <c r="L17" s="65"/>
+      <c r="M17" s="65"/>
     </row>
     <row r="18">
-      <c r="I18" s="51" t="s">
-        <v>223</v>
-      </c>
-      <c r="J18" s="61">
+      <c r="I18" s="53" t="s">
+        <v>229</v>
+      </c>
+      <c r="J18" s="63">
         <f>D10*B3</f>
         <v>82593000000</v>
       </c>
-      <c r="K18" s="61">
+      <c r="K18" s="63">
         <f>B4*D11</f>
         <v>28764590400</v>
       </c>
-      <c r="L18" s="61">
+      <c r="L18" s="63">
         <f>B5*D12</f>
         <v>72333000000</v>
       </c>
-      <c r="M18" s="61">
+      <c r="M18" s="63">
         <f>J18+K18+L18</f>
         <v>183690590400</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="49" t="s">
-        <v>267</v>
+      <c r="A20" s="51" t="s">
+        <v>273</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="3"/>
     </row>
     <row r="21">
-      <c r="A21" s="65" t="s">
-        <v>268</v>
-      </c>
-      <c r="B21" s="48">
+      <c r="A21" s="67" t="s">
+        <v>274</v>
+      </c>
+      <c r="B21" s="50">
         <v>1.0</v>
       </c>
-      <c r="C21" s="66" t="s">
-        <v>269</v>
+      <c r="C21" s="68" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="52" t="s">
-        <v>270</v>
-      </c>
-      <c r="B22" s="67">
+      <c r="A22" s="54" t="s">
+        <v>276</v>
+      </c>
+      <c r="B22" s="69">
         <v>2.0</v>
       </c>
-      <c r="C22" s="68"/>
+      <c r="C22" s="70"/>
     </row>
     <row r="23">
-      <c r="A23" s="69" t="s">
-        <v>271</v>
-      </c>
-      <c r="B23" s="52" t="s">
-        <v>272</v>
-      </c>
-      <c r="C23" s="52" t="s">
-        <v>273</v>
+      <c r="A23" s="71" t="s">
+        <v>277</v>
+      </c>
+      <c r="B23" s="54" t="s">
+        <v>278</v>
+      </c>
+      <c r="C23" s="54" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="70"/>
+      <c r="A24" s="72"/>
       <c r="B24" s="14">
         <v>47.0</v>
       </c>
@@ -7640,8 +7786,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="52" t="s">
-        <v>274</v>
+      <c r="A25" s="54" t="s">
+        <v>280</v>
       </c>
       <c r="B25" s="14">
         <v>12.0</v>
@@ -7651,8 +7797,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="52" t="s">
-        <v>275</v>
+      <c r="A26" s="54" t="s">
+        <v>281</v>
       </c>
       <c r="B26" s="14">
         <v>12.0</v>
@@ -7662,8 +7808,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="52" t="s">
-        <v>276</v>
+      <c r="A27" s="54" t="s">
+        <v>282</v>
       </c>
       <c r="B27" s="14">
         <v>12.0</v>
@@ -7673,8 +7819,8 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="52" t="s">
-        <v>277</v>
+      <c r="A28" s="54" t="s">
+        <v>283</v>
       </c>
       <c r="B28" s="14">
         <v>0.72</v>
@@ -7684,8 +7830,8 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="52" t="s">
-        <v>278</v>
+      <c r="A29" s="54" t="s">
+        <v>284</v>
       </c>
       <c r="B29" s="14">
         <v>8.5</v>
@@ -7695,8 +7841,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="52" t="s">
-        <v>279</v>
+      <c r="A30" s="54" t="s">
+        <v>285</v>
       </c>
       <c r="B30" s="14">
         <v>0.85</v>
@@ -7706,8 +7852,8 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="52" t="s">
-        <v>280</v>
+      <c r="A31" s="54" t="s">
+        <v>286</v>
       </c>
       <c r="B31" s="14">
         <v>2.5</v>
@@ -7717,45 +7863,45 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="49" t="s">
-        <v>281</v>
+      <c r="A34" s="51" t="s">
+        <v>287</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" s="3"/>
     </row>
     <row r="35">
-      <c r="A35" s="65" t="s">
-        <v>268</v>
-      </c>
-      <c r="B35" s="48">
+      <c r="A35" s="67" t="s">
+        <v>274</v>
+      </c>
+      <c r="B35" s="50">
         <v>1.0</v>
       </c>
-      <c r="C35" s="66" t="s">
-        <v>269</v>
+      <c r="C35" s="68" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="52" t="s">
-        <v>270</v>
-      </c>
-      <c r="B36" s="67">
+      <c r="A36" s="54" t="s">
+        <v>276</v>
+      </c>
+      <c r="B36" s="69">
         <v>2.0</v>
       </c>
-      <c r="C36" s="68"/>
+      <c r="C36" s="70"/>
     </row>
     <row r="37">
-      <c r="A37" s="69" t="s">
-        <v>271</v>
-      </c>
-      <c r="B37" s="52" t="s">
-        <v>272</v>
-      </c>
-      <c r="C37" s="52" t="s">
-        <v>273</v>
+      <c r="A37" s="71" t="s">
+        <v>277</v>
+      </c>
+      <c r="B37" s="54" t="s">
+        <v>278</v>
+      </c>
+      <c r="C37" s="54" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="70"/>
+      <c r="A38" s="72"/>
       <c r="B38" s="14">
         <v>20.0</v>
       </c>
@@ -7764,8 +7910,8 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="52" t="s">
-        <v>282</v>
+      <c r="A39" s="54" t="s">
+        <v>288</v>
       </c>
       <c r="B39" s="14">
         <v>0.0</v>
@@ -7775,8 +7921,8 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="52" t="s">
-        <v>283</v>
+      <c r="A40" s="54" t="s">
+        <v>289</v>
       </c>
       <c r="B40" s="14">
         <v>0.0</v>
@@ -7786,8 +7932,8 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="52" t="s">
-        <v>274</v>
+      <c r="A41" s="54" t="s">
+        <v>280</v>
       </c>
       <c r="B41" s="14">
         <v>4.9</v>
@@ -7797,8 +7943,8 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="52" t="s">
-        <v>275</v>
+      <c r="A42" s="54" t="s">
+        <v>281</v>
       </c>
       <c r="B42" s="14">
         <v>4.9</v>
@@ -7808,8 +7954,8 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="52" t="s">
-        <v>276</v>
+      <c r="A43" s="54" t="s">
+        <v>282</v>
       </c>
       <c r="B43" s="14">
         <v>4.9</v>
@@ -7819,8 +7965,8 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="52" t="s">
-        <v>284</v>
+      <c r="A44" s="54" t="s">
+        <v>290</v>
       </c>
       <c r="B44" s="14">
         <v>0.0</v>
@@ -7830,8 +7976,8 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="52" t="s">
-        <v>285</v>
+      <c r="A45" s="54" t="s">
+        <v>291</v>
       </c>
       <c r="B45" s="14">
         <v>26.0</v>
@@ -7841,12 +7987,12 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="71"/>
-      <c r="B46" s="71"/>
-      <c r="C46" s="71"/>
+      <c r="A46" s="73"/>
+      <c r="B46" s="73"/>
+      <c r="C46" s="73"/>
     </row>
     <row r="47">
-      <c r="A47" s="72"/>
+      <c r="A47" s="74"/>
       <c r="B47" s="10"/>
       <c r="C47" s="10"/>
     </row>
@@ -7895,185 +8041,185 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="71"/>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
+      <c r="A1" s="73"/>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
     </row>
     <row r="2">
-      <c r="A2" s="71"/>
-      <c r="B2" s="71"/>
-      <c r="C2" s="71"/>
-      <c r="D2" s="73"/>
+      <c r="A2" s="73"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="75"/>
     </row>
     <row r="3">
       <c r="A3" s="10"/>
-      <c r="B3" s="74"/>
-      <c r="D3" s="74"/>
+      <c r="B3" s="76"/>
+      <c r="D3" s="76"/>
     </row>
     <row r="5">
-      <c r="C5" s="49" t="s">
-        <v>286</v>
+      <c r="C5" s="51" t="s">
+        <v>292</v>
       </c>
       <c r="D5" s="2"/>
-      <c r="E5" s="49" t="s">
-        <v>287</v>
+      <c r="E5" s="51" t="s">
+        <v>293</v>
       </c>
       <c r="F5" s="2"/>
-      <c r="G5" s="49" t="s">
-        <v>288</v>
+      <c r="G5" s="51" t="s">
+        <v>294</v>
       </c>
       <c r="H5" s="3"/>
-      <c r="I5" s="75"/>
-      <c r="J5" s="75"/>
-      <c r="K5" s="75"/>
+      <c r="I5" s="77"/>
+      <c r="J5" s="77"/>
+      <c r="K5" s="77"/>
     </row>
     <row r="6">
-      <c r="B6" s="76" t="s">
-        <v>289</v>
-      </c>
-      <c r="C6" s="76" t="s">
-        <v>290</v>
-      </c>
-      <c r="D6" s="76" t="s">
-        <v>291</v>
-      </c>
-      <c r="E6" s="76" t="s">
-        <v>290</v>
-      </c>
-      <c r="F6" s="76" t="s">
-        <v>291</v>
-      </c>
-      <c r="G6" s="77" t="s">
-        <v>290</v>
-      </c>
-      <c r="H6" s="77" t="s">
-        <v>291</v>
-      </c>
-      <c r="I6" s="51" t="s">
-        <v>292</v>
-      </c>
-      <c r="J6" s="76" t="s">
-        <v>293</v>
-      </c>
-      <c r="K6" s="78" t="s">
-        <v>294</v>
-      </c>
-      <c r="L6" s="76" t="s">
+      <c r="B6" s="78" t="s">
         <v>295</v>
       </c>
-      <c r="M6" s="76" t="s">
+      <c r="C6" s="78" t="s">
         <v>296</v>
       </c>
-      <c r="N6" s="50" t="s">
+      <c r="D6" s="78" t="s">
         <v>297</v>
       </c>
+      <c r="E6" s="78" t="s">
+        <v>296</v>
+      </c>
+      <c r="F6" s="78" t="s">
+        <v>297</v>
+      </c>
+      <c r="G6" s="79" t="s">
+        <v>296</v>
+      </c>
+      <c r="H6" s="79" t="s">
+        <v>297</v>
+      </c>
+      <c r="I6" s="53" t="s">
+        <v>298</v>
+      </c>
+      <c r="J6" s="78" t="s">
+        <v>299</v>
+      </c>
+      <c r="K6" s="80" t="s">
+        <v>300</v>
+      </c>
+      <c r="L6" s="78" t="s">
+        <v>301</v>
+      </c>
+      <c r="M6" s="78" t="s">
+        <v>302</v>
+      </c>
+      <c r="N6" s="52" t="s">
+        <v>303</v>
+      </c>
     </row>
     <row r="7">
-      <c r="B7" s="79">
+      <c r="B7" s="81">
         <v>0.0</v>
       </c>
-      <c r="C7" s="80">
+      <c r="C7" s="82">
         <v>0.0</v>
       </c>
-      <c r="D7" s="80">
+      <c r="D7" s="82">
         <v>0.0</v>
       </c>
-      <c r="E7" s="80">
+      <c r="E7" s="82">
         <v>0.0</v>
       </c>
-      <c r="F7" s="80">
+      <c r="F7" s="82">
         <v>0.0</v>
       </c>
-      <c r="G7" s="80">
+      <c r="G7" s="82">
         <v>0.0</v>
       </c>
-      <c r="H7" s="57">
+      <c r="H7" s="59">
         <v>0.0</v>
       </c>
-      <c r="I7" s="57">
+      <c r="I7" s="59">
         <f t="shared" ref="I7:I8" si="1">(C7-D7)+(E7+F7)+(G7-H7)</f>
         <v>0</v>
       </c>
-      <c r="J7" s="81">
+      <c r="J7" s="83">
         <f>Presupuesto!Q53</f>
         <v>1016016859</v>
       </c>
       <c r="K7" s="10">
         <v>0.0</v>
       </c>
-      <c r="L7" s="79">
+      <c r="L7" s="81">
         <v>0.0</v>
       </c>
-      <c r="M7" s="81">
+      <c r="M7" s="83">
         <f t="shared" ref="M7:M8" si="2">I7-J7-K7-L7</f>
         <v>-1016016859</v>
       </c>
-      <c r="N7" s="58">
+      <c r="N7" s="60">
         <f>M7</f>
         <v>-1016016859</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="79">
+      <c r="B8" s="81">
         <v>1.0</v>
       </c>
-      <c r="C8" s="80">
+      <c r="C8" s="82">
         <f>APU!B3*APU!C10</f>
         <v>152950000000</v>
       </c>
-      <c r="D8" s="82">
+      <c r="D8" s="84">
         <f>APU!J18</f>
         <v>82593000000</v>
       </c>
-      <c r="E8" s="80">
+      <c r="E8" s="82">
         <f>APU!B4*APU!C11</f>
         <v>53267760000</v>
       </c>
-      <c r="F8" s="82">
+      <c r="F8" s="84">
         <f>APU!K18</f>
         <v>28764590400</v>
       </c>
-      <c r="G8" s="80">
+      <c r="G8" s="82">
         <f>APU!B5*APU!C12</f>
         <v>133950000000</v>
       </c>
-      <c r="H8" s="82">
+      <c r="H8" s="84">
         <f>APU!L18</f>
         <v>72333000000</v>
       </c>
-      <c r="I8" s="57">
+      <c r="I8" s="59">
         <f t="shared" si="1"/>
         <v>214006350400</v>
       </c>
-      <c r="J8" s="79">
+      <c r="J8" s="81">
         <v>0.0</v>
       </c>
-      <c r="K8" s="79">
+      <c r="K8" s="81">
         <v>0.0</v>
       </c>
-      <c r="L8" s="79">
+      <c r="L8" s="81">
         <v>0.0</v>
       </c>
-      <c r="M8" s="81">
+      <c r="M8" s="83">
         <f t="shared" si="2"/>
         <v>214006350400</v>
       </c>
-      <c r="N8" s="58">
+      <c r="N8" s="60">
         <f>N7+M8</f>
         <v>212990333542</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="10"/>
-      <c r="B9" s="83"/>
+      <c r="B9" s="85"/>
     </row>
     <row r="14">
-      <c r="A14" s="47" t="s">
-        <v>224</v>
-      </c>
-      <c r="B14" s="84" t="s">
-        <v>298</v>
+      <c r="A14" s="49" t="s">
+        <v>230</v>
+      </c>
+      <c r="B14" s="86" t="s">
+        <v>304</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
